--- a/output/pdf_financials_xlsx/GGC.xlsx
+++ b/output/pdf_financials_xlsx/GGC.xlsx
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.420217</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.720289</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.139869</v>
       </c>
     </row>
     <row r="93">
@@ -2894,7 +2894,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>1.420217</v>
       </c>

--- a/output/pdf_financials_xlsx/GGC.xlsx
+++ b/output/pdf_financials_xlsx/GGC.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.030482</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017447</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.964602</v>
+        <v>-0.995084</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.502846</v>
+        <v>-0.520293</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.415263</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.964602</v>
+        <v>-0.995084</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.502846</v>
+        <v>-0.520293</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.415263</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">

--- a/output/pdf_financials_xlsx/GGC.xlsx
+++ b/output/pdf_financials_xlsx/GGC.xlsx
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.031958</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.995084</v>
+        <v>-0.963126</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.520293</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.031958</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -3334,7 +3334,11 @@
           <t>Depreciation of right of use assets</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.031958</v>
       </c>

--- a/output/pdf_financials_xlsx/GGC.xlsx
+++ b/output/pdf_financials_xlsx/GGC.xlsx
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.2025</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.2025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="68">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.2025</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.2025</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="69">
